--- a/artfynd/S 4093-2022 artfynd.xlsx
+++ b/artfynd/S 4093-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746979</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746982</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746980</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746981</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746988</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746985</t>
         </is>
       </c>
     </row>
@@ -1600,6 +1645,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581049</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581050</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2246,6 +2321,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581051</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2357,6 +2437,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581052</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2463,6 +2548,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581056</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581059</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130581057</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746983</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,8 +2992,36 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746984</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>